--- a/apartments.xlsx
+++ b/apartments.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Объявления" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$I$1:$I$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$I$1:$I$99</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="401">
   <si>
     <t>ID</t>
   </si>
@@ -57,32 +57,12 @@
     <t>+7 922 472-06-67</t>
   </si>
   <si>
-    <t>Однокомнатные номера на первом и втором этажах с размещением от 2 и 5 гостей. На территории есть:
-💥 Стационарный бассейн 4м×3м🏊‍♂🏄‍♀;
-💥 Мангальная зона🍖;
-💥 Беседка🍹🍸;
-Для маленьких гостей:
-💥 Небольшая детская площадка🧸;
-💥Качель 🎠;
-💥Батуты🤸‍♀;</t>
-  </si>
-  <si>
     <t>2-комн</t>
   </si>
   <si>
     <t>Светлана</t>
   </si>
   <si>
-    <t>Двухкомнатные номера размещением до 6 человек. На территории есть:
-💥 Стационарный бассейн 4м×3м🏊‍♂🏄‍♀;
-💥 Мангальная зона🍖;
-💥 Беседка🍹🍸;
-Для маленьких гостей:
-💥 Небольшая детская площадка🧸;
-💥Качель 🎠;
-💥Батуты🤸‍♀;</t>
-  </si>
-  <si>
     <t>по запросу</t>
   </si>
   <si>
@@ -90,9 +70,6 @@
   </si>
   <si>
     <t>частный дом</t>
-  </si>
-  <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_75819</t>
   </si>
   <si>
     <t>+7 988 570-64-42</t>
@@ -681,9 +658,6 @@
 🌊 До центрального пляжа 10 минут езды, где также расположена приморская набережная со всеми развлечениями для детей и взрослых(парки с аттракционами, дельфинарий, океанариум, аквапарк, кафе с живой музыкой, сувенирная продукция)</t>
   </si>
   <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_70056</t>
-  </si>
-  <si>
     <t>В доме на каждом этаже: кухня, холодильник, сплит система, телевизор, санузел, душ. Стиральная машина. Большой двор,беседка, мангал. Место для двух автомобилей</t>
   </si>
   <si>
@@ -697,20 +671,7 @@
 На 1 этаже дома расположен « Магнит косметик» и «Пятерочка»</t>
   </si>
   <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_69407</t>
-  </si>
-  <si>
     <t>Лейла</t>
-  </si>
-  <si>
-    <t>Кухня, санузел-в доме.
-Посуда
-стиральная машина
-ТВ
-интернет
-кондиционер.
-Мангал и шампура.
-Животные по договорённости.</t>
   </si>
   <si>
     <t>https://vk.com/eysk_aparts?w=wall-109406141_74887</t>
@@ -1460,6 +1421,109 @@
 • Мини-холодильник для ваших напитков и закусок
 • Душ и туалет для вашего удобства
 • Постельные принадлежности и полотенца</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76033</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76031</t>
+  </si>
+  <si>
+    <t>Мария</t>
+  </si>
+  <si>
+    <t>Сдаем уютные 2-х, 3-х и 4-х местные комнаты. В каждой есть всё необходимое: кондиционер, телевизор, холодильник, Wi-Fi, чистое белье.</t>
+  </si>
+  <si>
+    <t>+7 911 716-31-99</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76030</t>
+  </si>
+  <si>
+    <t>+7 906 763-81-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сергей </t>
+  </si>
+  <si>
+    <t>• В каждом номере:
+Кондиционер, ТВ, Wi-Fi
+Мини-кухня с посудой
+Холодильник, постельное бельё, полотенца, пледы
+• Общие удобства:
+Стиральная машина, утюг, гладильная доска
+Фены, отдельное помещение для хранения</t>
+  </si>
+  <si>
+    <t>Валерия</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_75950</t>
+  </si>
+  <si>
+    <t>+7 961 854-18-66</t>
+  </si>
+  <si>
+    <t>🌿 Территория и удобства:
+Большой, зелёный, ухоженный двор
+Две зоны отдыха
+Мангал
+Много детских игрушек
+По запросу – установка детской кроватки
+Бассейна нет</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_75947</t>
+  </si>
+  <si>
+    <t>🏡 Новый гостевой дом в Ейске!
+🛏 Всё новое и комфортное!
+В каждом номере:
+душ и туалет
+сплит-система
+телевизор и интернет
+холодильник и посуда
+терраса с кофейными столиками
+🌿 На территории:
+мангальная зона и летняя кухня-беседка (с посудой и печью)
+детская площадка 👶
+детский бассейн 💦</t>
+  </si>
+  <si>
+    <t>+7 914 172-37-46</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_75942</t>
+  </si>
+  <si>
+    <t>кондиционеры / сплит-системы
+ТВ, Wi-Fi
+кухня с полной комплектацией посуды
+холодильник, СВЧ
+стиральная машина
+горячая и холодная вода — круглосуточно
+постельное бельё и полотенца предоставляются
+фен, утюг, гладильная доска
+🌿 На территории: беседка, зона отдыха, мангал и шампура
+парковка у дома.</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_75932</t>
+  </si>
+  <si>
+    <t>Однокомнатные номера на первом и втором этажах с размещением от 2 и 5 гостей.
+Двухкомнатные номера размещением до 6 человек. ✨
+Для вас на территории есть:
+💥 Стационарный бассейн 4м×3м🏊‍♂🏄‍♀;
+💥 Мангальная зона🍖;
+💥 Беседка🍹🍸;
+Для маленьких гостей:
+💥 Небольшая детская площадка🧸;
+💥Качель 🎠;
+💥Батуты🤸‍♀;
+📍В номерах на втором этаже есть всё необходимое для комфортного отдыха: Кухня, холодильник, чайник, посуда.
+Двуспальная кровать и двуспальный диван, тв, кондиционер, с/у и душ. К каждому номеру на балконе стол и сушилка для белья.</t>
   </si>
 </sst>
 </file>
@@ -1870,7 +1934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1879,7 +1943,7 @@
     <col min="4" max="4" width="12.88671875" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="48.109375" customWidth="1"/>
+    <col min="7" max="7" width="50.44140625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="20.33203125" style="13" customWidth="1"/>
     <col min="10" max="10" width="62.44140625" style="7" customWidth="1"/>
@@ -1890,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1911,30 +1975,30 @@
         <v>6</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2">
         <v>1000</v>
       </c>
       <c r="E2" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
@@ -1943,260 +2007,260 @@
         <v>10</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" s="5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2">
+        <v>100</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D4" s="2">
+        <v>550</v>
+      </c>
+      <c r="E4" s="2">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2">
-        <v>100</v>
-      </c>
-      <c r="E4" s="2">
-        <v>4</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2">
         <v>550</v>
       </c>
       <c r="E5" s="2">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>6</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
       <c r="B6" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="E6" s="2">
         <v>4</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="E7" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2">
         <v>300</v>
       </c>
       <c r="E8" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E9" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D10" s="2">
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="E10" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>33</v>
@@ -2205,123 +2269,123 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D11" s="2">
-        <v>550</v>
+        <v>250</v>
       </c>
       <c r="E11" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D12" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D13" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E13" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J13" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D14" s="2">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="E14" s="2">
         <v>4</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>53</v>
@@ -2329,409 +2393,409 @@
       <c r="I14" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D15" s="2">
         <v>700</v>
       </c>
       <c r="E15" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>58</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="2">
+        <v>350</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
         <v>17</v>
       </c>
-      <c r="D16" s="2">
-        <v>700</v>
-      </c>
-      <c r="E16" s="2">
-        <v>8</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
       <c r="B17" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="E17" s="2">
         <v>4</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D18" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E18" s="2">
         <v>4</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G18" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="I18" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="J18" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J18" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D19" s="2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E19" s="2">
         <v>4</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>71</v>
+        <v>13</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="2">
-        <v>300</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2">
         <v>4</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>75</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="D21" s="2">
+        <v>50</v>
       </c>
       <c r="E21" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>78</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I21" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="I21" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J21" s="10" t="s">
+      <c r="J21" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D22" s="2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="E22" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>83</v>
+      <c r="J22" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E23" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D24" s="2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E24" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>90</v>
+        <v>376</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>89</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>91</v>
+        <v>375</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D25" s="2">
-        <v>400</v>
-      </c>
-      <c r="E25" s="2">
-        <v>7</v>
+        <v>150</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>382</v>
+        <v>91</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D26" s="2">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="E26">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>94</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D27" s="2">
-        <v>70</v>
+        <v>550</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>97</v>
@@ -2740,103 +2804,103 @@
         <v>98</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="J27" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D28" s="2">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>100</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="J28" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="I28" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D29" s="2">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>139</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D30" s="2">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="E30">
         <v>4</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G30" s="9" t="s">
         <v>109</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="J30" s="7" t="s">
         <v>110</v>
@@ -2844,470 +2908,470 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D31" s="2">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>112</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D32" s="2">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E32">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="H32" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="I32" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J32" s="10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D33" s="2">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>34</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="2">
+        <v>50</v>
+      </c>
+      <c r="E34">
         <v>5</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I33" s="12" t="s">
+      <c r="F34" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>35</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
         <v>36</v>
       </c>
-      <c r="J33" s="10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="2">
+      <c r="B36" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="2">
         <v>400</v>
-      </c>
-      <c r="E34">
-        <v>4</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="2">
-        <v>50</v>
-      </c>
-      <c r="E35">
-        <v>5</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D36" s="2">
-        <v>1000</v>
       </c>
       <c r="E36">
         <v>4</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>132</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D37" s="2">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="E37">
         <v>4</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D38" s="2">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I38" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="I38" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J38" s="7" t="s">
+      <c r="J38" s="10" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D39" s="2">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="E39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>146</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I39" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J39" s="10" t="s">
+    </row>
+    <row r="40" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="2">
+        <v>300</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="9" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="2">
-        <v>100</v>
-      </c>
-      <c r="E40">
-        <v>6</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G40" s="9" t="s">
+      <c r="H40" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="I40" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="J40" s="7" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J40" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E41">
         <v>4</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>42</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G41" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D42" s="2">
-        <v>900</v>
+        <v>30</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>156</v>
+        <v>211</v>
       </c>
       <c r="I42" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="J42" s="10" t="s">
-        <v>158</v>
+      <c r="J42" s="7" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2">
-        <v>30</v>
+        <v>700</v>
       </c>
       <c r="E43">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D44" s="2">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E44">
         <v>4</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>168</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="J44" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J44" s="10" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D45" s="2">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>170</v>
@@ -3316,30 +3380,30 @@
         <v>171</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J45" s="10" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D46" s="2">
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="E46">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>173</v>
@@ -3348,501 +3412,501 @@
         <v>174</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="J46" s="10" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D47" s="2">
         <v>50</v>
       </c>
       <c r="E47">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2">
+        <v>800</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G47" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I47" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J47" s="10" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="2">
+      <c r="D49" s="2">
+        <v>350</v>
+      </c>
+      <c r="E49">
+        <v>8</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
         <v>50</v>
       </c>
-      <c r="E48">
+      <c r="B50" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="2">
+        <v>800</v>
+      </c>
+      <c r="E50">
         <v>9</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F50" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G48" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2">
-        <v>800</v>
-      </c>
-      <c r="E49">
+      <c r="D51">
+        <v>100</v>
+      </c>
+      <c r="E51">
         <v>4</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="I49" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="2">
-        <v>350</v>
-      </c>
-      <c r="E50">
-        <v>8</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="I50" s="12" t="s">
+      <c r="F51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="J50" s="10" t="s">
+      <c r="H51" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J51" s="10" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="2">
-        <v>800</v>
-      </c>
-      <c r="E51">
-        <v>9</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="I51" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52">
-        <v>100</v>
+        <v>11</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1000</v>
       </c>
       <c r="E52">
         <v>4</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J52" s="10" t="s">
-        <v>192</v>
+        <v>144</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D53" s="2">
-        <v>1000</v>
+        <v>37</v>
+      </c>
+      <c r="D53">
+        <v>300</v>
       </c>
       <c r="E53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D54">
-        <v>300</v>
+        <v>37</v>
+      </c>
+      <c r="D54" s="2">
+        <v>750</v>
       </c>
       <c r="E54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>196</v>
       </c>
       <c r="H54" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I54" s="12" t="s">
         <v>197</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="J54" s="7" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D55" s="2">
-        <v>750</v>
+        <v>37</v>
+      </c>
+      <c r="D55">
+        <v>70</v>
       </c>
       <c r="E55">
         <v>4</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>56</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" s="2">
+        <v>800</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H56" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>58</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" s="2">
+        <v>350</v>
+      </c>
+      <c r="E57">
+        <v>4</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="J57" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="I55" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D56">
-        <v>70</v>
-      </c>
-      <c r="E56">
-        <v>4</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D57" s="2">
-        <v>800</v>
-      </c>
-      <c r="E57">
-        <v>3</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="I57" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D58" s="2">
-        <v>350</v>
+        <v>15</v>
+      </c>
+      <c r="D58">
+        <v>250</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>212</v>
+        <v>65</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59">
-        <v>250</v>
+        <v>37</v>
+      </c>
+      <c r="D59" s="2">
+        <v>350</v>
       </c>
       <c r="E59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>68</v>
+        <v>212</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D60" s="2">
-        <v>350</v>
+        <v>37</v>
+      </c>
+      <c r="D60">
+        <v>100</v>
       </c>
       <c r="E60">
         <v>4</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G60" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="J60" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D61">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E61">
         <v>4</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>225</v>
+        <v>216</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D62">
         <v>1000</v>
@@ -3851,603 +3915,603 @@
         <v>4</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G62" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="J62" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63">
+        <v>700</v>
+      </c>
+      <c r="E63">
         <v>8</v>
       </c>
-      <c r="D63">
-        <v>1000</v>
-      </c>
-      <c r="E63">
-        <v>4</v>
-      </c>
       <c r="F63" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I63" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" s="7" t="s">
         <v>226</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D64">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E64">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G64" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J64" s="7" t="s">
         <v>230</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D65">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D66">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="E66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>238</v>
+        <v>23</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D67">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="E67">
+        <v>5</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>69</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68">
+        <v>800</v>
+      </c>
+      <c r="E68">
         <v>4</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="F68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>70</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G67" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="I67" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J67" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
-        <v>68</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D68">
-        <v>300</v>
-      </c>
-      <c r="E68">
-        <v>5</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2">
-        <v>69</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D69">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>248</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="I69" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J69" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="J69" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D70">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E70">
         <v>6</v>
       </c>
       <c r="F70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I70" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>72</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G70" s="9" t="s">
+      <c r="D71">
+        <v>1000</v>
+      </c>
+      <c r="E71">
+        <v>15</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J71" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="H70" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I70" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="J70" s="7" t="s">
+    </row>
+    <row r="72" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>73</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72">
+        <v>400</v>
+      </c>
+      <c r="E72">
+        <v>5</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="9" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
-        <v>71</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71">
-        <v>450</v>
-      </c>
-      <c r="E71">
-        <v>6</v>
-      </c>
-      <c r="F71" s="2" t="s">
+      <c r="H72" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I72" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>74</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G71" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="H71" s="3" t="s">
+      <c r="D73">
+        <v>150</v>
+      </c>
+      <c r="E73">
+        <v>4</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="I71" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J71" s="10" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
-        <v>72</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72">
-        <v>1000</v>
-      </c>
-      <c r="E72">
-        <v>15</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G72" s="9" t="s">
+      <c r="H73" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J72" s="10" t="s">
+      <c r="I73" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J73" s="10" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
-        <v>73</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D73">
-        <v>400</v>
-      </c>
-      <c r="E73">
-        <v>5</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="I73" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="J73" s="10" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D74">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E74">
         <v>4</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="G74" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="J74" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="I74" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D75">
-        <v>1200</v>
+        <v>20</v>
       </c>
       <c r="E75">
         <v>4</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>269</v>
+        <v>12</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D76">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E76">
         <v>4</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>376</v>
+        <v>268</v>
       </c>
       <c r="I76" s="12" t="s">
-        <v>13</v>
+        <v>144</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D77">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E77">
         <v>4</v>
       </c>
       <c r="F77" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J77" s="10" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>79</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G77" s="9" t="s">
+      <c r="D78">
+        <v>1200</v>
+      </c>
+      <c r="E78">
+        <v>8</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="H77" s="3" t="s">
+      <c r="H78" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="I77" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="J77" s="10" t="s">
+      <c r="I78" s="12" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
-        <v>78</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D78">
-        <v>150</v>
-      </c>
-      <c r="E78">
+      <c r="J78" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>80</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79">
+        <v>50</v>
+      </c>
+      <c r="E79">
         <v>4</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="H78" s="3" t="s">
+      <c r="F79" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="I78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="10" t="s">
+      <c r="H79" s="3" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2">
-        <v>79</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D79">
-        <v>1200</v>
-      </c>
-      <c r="E79">
-        <v>8</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G79" s="9" t="s">
+      <c r="J79" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="H79" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="I79" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="J79" s="10" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D80">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E80">
         <v>4</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
+      </c>
+      <c r="I80" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D81">
         <v>500</v>
@@ -4456,954 +4520,1070 @@
         <v>4</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="J81" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="H81" s="3" t="s">
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>83</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D82">
+        <v>400</v>
+      </c>
+      <c r="E82">
+        <v>6</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G82" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="I81" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="J81" s="10" t="s">
+      <c r="H82" s="3" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="2">
-        <v>82</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D82">
-        <v>500</v>
-      </c>
-      <c r="E82">
+      <c r="I82" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>84</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83">
+        <v>750</v>
+      </c>
+      <c r="E83">
         <v>4</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="H82" s="3" t="s">
+      <c r="F83" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="H83" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="I82" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="J82" s="10" t="s">
+      <c r="I83" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J83" s="10" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
-        <v>83</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D83">
-        <v>400</v>
-      </c>
-      <c r="E83">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>85</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D84">
+        <v>50</v>
+      </c>
+      <c r="E84">
         <v>6</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G83" s="9" t="s">
+      <c r="F84" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="H84" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="I83" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J83" s="7" t="s">
+      <c r="I84" s="12" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
-        <v>84</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D84">
-        <v>750</v>
-      </c>
-      <c r="E84">
-        <v>4</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="H84" s="3" t="s">
+      <c r="J84" s="7" t="s">
         <v>296</v>
-      </c>
-      <c r="I84" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J84" s="10" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D85">
-        <v>50</v>
-      </c>
-      <c r="E85">
-        <v>6</v>
+        <v>900</v>
       </c>
       <c r="F85" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="I85" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>88</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G85" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="H85" s="3" t="s">
+      <c r="D86">
         <v>300</v>
       </c>
-      <c r="I85" s="12" t="s">
+      <c r="E86">
+        <v>5</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="J85" s="7" t="s">
+      <c r="H86" s="3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
-        <v>86</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D86">
-        <v>900</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G86" s="9" t="s">
+      <c r="I86" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="H86" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="I86" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D87">
         <v>300</v>
       </c>
       <c r="E87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J87" s="10" t="s">
-        <v>309</v>
+        <v>17</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D88">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E88">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="I88" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>91</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G88" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="H88" s="3" t="s">
+      <c r="D89">
+        <v>800</v>
+      </c>
+      <c r="E89">
+        <v>6</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="I88" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J88" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
-        <v>90</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89">
-        <v>100</v>
-      </c>
-      <c r="E89">
-        <v>5</v>
-      </c>
-      <c r="F89" s="2" t="s">
+      <c r="H89" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="I89" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J89" s="10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>92</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G89" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="I89" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="J89" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
-        <v>91</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D90">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="E90">
         <v>6</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="I90" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J90" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D91">
+        <v>300</v>
+      </c>
+      <c r="E91">
+        <v>4</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I91" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>94</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92">
+        <v>500</v>
+      </c>
+      <c r="E92">
+        <v>9</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="I92" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="J92" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>95</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D93">
         <v>50</v>
       </c>
-      <c r="E91">
-        <v>6</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="I91" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="J91" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <v>93</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D92">
-        <v>300</v>
-      </c>
-      <c r="E92">
+      <c r="E93">
         <v>4</v>
       </c>
-      <c r="F92" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G92" s="9" t="s">
+      <c r="F93" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="H92" s="3" t="s">
+      <c r="H93" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="I93" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" s="10" t="s">
         <v>321</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J92" s="7" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
-        <v>94</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D93">
-        <v>500</v>
-      </c>
-      <c r="E93">
-        <v>9</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I93" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="J93" s="10" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D94">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>326</v>
+        <v>377</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>339</v>
+        <v>168</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>26</v>
+        <v>378</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D95">
         <v>500</v>
       </c>
       <c r="E95">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D96">
         <v>500</v>
       </c>
       <c r="E96">
+        <v>4</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I96" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="J96" s="10" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>99</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D97">
+        <v>350</v>
+      </c>
+      <c r="E97">
         <v>7</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="F97" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="I97" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="J97" s="10" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>100</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G96" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I96" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="J96" s="10" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H97" s="3"/>
-    </row>
-    <row r="98" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
-        <v>98</v>
-      </c>
-      <c r="B98" s="2" t="s">
+      <c r="D98">
+        <v>400</v>
+      </c>
+      <c r="E98">
+        <v>10</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="I98" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="J98" s="10" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>101</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D99">
+        <v>800</v>
+      </c>
+      <c r="E99">
+        <v>5</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="I99" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="J99" s="10" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="12"/>
+      <c r="J100" s="10"/>
+    </row>
+    <row r="101" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="9"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="12"/>
+      <c r="J101" s="10"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H102" s="3"/>
+    </row>
+    <row r="103" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103">
+        <v>300</v>
+      </c>
+      <c r="E103">
+        <v>6</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="I103" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="J103" s="10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D104">
+        <v>900</v>
+      </c>
+      <c r="E104">
+        <v>3</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="I104" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="J104" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D98">
-        <v>300</v>
-      </c>
-      <c r="E98">
-        <v>6</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I98" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="J98" s="10" t="s">
+    </row>
+    <row r="105" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D105">
+        <v>900</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="8" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
-        <v>99</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D99">
-        <v>900</v>
-      </c>
-      <c r="E99">
-        <v>3</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G99" s="8" t="s">
+      <c r="H105" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="H99" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="I99" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="J99" s="7" t="s">
+      <c r="I105" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J105" s="10" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="2">
-        <v>100</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D100">
-        <v>900</v>
-      </c>
-      <c r="E100">
-        <v>2</v>
-      </c>
-      <c r="F100" s="2" t="s">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G100" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="I100" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J100" s="10" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A101" s="2">
-        <v>101</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D101">
+      <c r="D106">
         <v>1000</v>
       </c>
-      <c r="E101">
+      <c r="E106">
         <v>8</v>
       </c>
-      <c r="F101" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G101" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="I101" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="J101" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="2">
+      <c r="F106" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I106" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D102">
-        <v>350</v>
-      </c>
-      <c r="E102">
-        <v>5</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G102" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="I102" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="J102" s="10" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A103" s="2">
-        <v>103</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D103">
-        <v>1000</v>
-      </c>
-      <c r="E103">
-        <v>4</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G103" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="I103" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J103" s="7" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="2">
-        <v>104</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D104">
-        <v>1200</v>
-      </c>
-      <c r="E104">
-        <v>4</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G104" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="I104" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="J104" s="10" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A105" s="2">
-        <v>105</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D105">
-        <v>950</v>
-      </c>
-      <c r="E105">
-        <v>4</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G105" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I105" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J105" s="7" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="2">
-        <v>106</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D106">
-        <v>600</v>
-      </c>
-      <c r="E106">
-        <v>7</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G106" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="I106" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="J106" s="10" t="s">
-        <v>360</v>
+      <c r="J106" s="7" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D107">
-        <v>1900</v>
+        <v>350</v>
       </c>
       <c r="E107">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108">
+        <v>1000</v>
+      </c>
+      <c r="E108">
+        <v>4</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I108" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="J108" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
         <v>108</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D108">
-        <v>450</v>
-      </c>
-      <c r="E108">
-        <v>5</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G108" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="I108" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="J108" s="7" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A109" s="2">
-        <v>109</v>
-      </c>
       <c r="B109" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D109">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="E109">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="J109" s="7" t="s">
-        <v>370</v>
+        <v>295</v>
+      </c>
+      <c r="J109" s="10" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D110">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="E110">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="I110" s="13" t="s">
-        <v>147</v>
+        <v>30</v>
       </c>
       <c r="J110" s="7" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111">
+        <v>600</v>
+      </c>
+      <c r="E111">
+        <v>7</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="I111" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J111" s="10" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
         <v>111</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D111">
+      <c r="B112" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112">
+        <v>1900</v>
+      </c>
+      <c r="E112">
+        <v>5</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I112" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J112" s="10" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D113">
+        <v>450</v>
+      </c>
+      <c r="E113">
+        <v>5</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="I113" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114">
+        <v>1700</v>
+      </c>
+      <c r="E114">
+        <v>6</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I114" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J114" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115">
+        <v>900</v>
+      </c>
+      <c r="E115">
+        <v>6</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="I115" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="J115" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116">
         <v>1600</v>
       </c>
-      <c r="E111">
+      <c r="E116">
         <v>5</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G111" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="I111" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="J111" s="10" t="s">
-        <v>375</v>
+      <c r="F116" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I116" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="J116" s="10" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="I1:I96"/>
+  <autoFilter ref="I1:I99"/>
   <hyperlinks>
-    <hyperlink ref="G17" r:id="rId1"/>
-    <hyperlink ref="G18" r:id="rId2"/>
+    <hyperlink ref="G16" r:id="rId1"/>
+    <hyperlink ref="G17" r:id="rId2"/>
     <hyperlink ref="G2" r:id="rId3"/>
     <hyperlink ref="G3" r:id="rId4"/>
     <hyperlink ref="G4" r:id="rId5"/>
@@ -5418,7 +5598,7 @@
     <hyperlink ref="G13" r:id="rId14"/>
     <hyperlink ref="G14" r:id="rId15"/>
     <hyperlink ref="G15" r:id="rId16"/>
-    <hyperlink ref="G16" r:id="rId17"/>
+    <hyperlink ref="G18" r:id="rId17"/>
     <hyperlink ref="G19" r:id="rId18"/>
     <hyperlink ref="G20" r:id="rId19"/>
     <hyperlink ref="G21" r:id="rId20"/>
@@ -5494,25 +5674,28 @@
     <hyperlink ref="G91" r:id="rId90"/>
     <hyperlink ref="G92" r:id="rId91"/>
     <hyperlink ref="G93" r:id="rId92"/>
-    <hyperlink ref="G94" r:id="rId93"/>
-    <hyperlink ref="G98" r:id="rId94"/>
-    <hyperlink ref="G99" r:id="rId95"/>
-    <hyperlink ref="G100" r:id="rId96"/>
-    <hyperlink ref="G101" r:id="rId97"/>
-    <hyperlink ref="G102" r:id="rId98"/>
-    <hyperlink ref="G103" r:id="rId99"/>
-    <hyperlink ref="G104" r:id="rId100"/>
-    <hyperlink ref="G105" r:id="rId101"/>
-    <hyperlink ref="G106" r:id="rId102"/>
-    <hyperlink ref="G107" r:id="rId103"/>
-    <hyperlink ref="G108" r:id="rId104"/>
-    <hyperlink ref="G109" r:id="rId105"/>
-    <hyperlink ref="G110" r:id="rId106"/>
-    <hyperlink ref="G111" r:id="rId107"/>
+    <hyperlink ref="G103" r:id="rId93"/>
+    <hyperlink ref="G104" r:id="rId94"/>
+    <hyperlink ref="G105" r:id="rId95"/>
+    <hyperlink ref="G106" r:id="rId96"/>
+    <hyperlink ref="G107" r:id="rId97"/>
+    <hyperlink ref="G108" r:id="rId98"/>
+    <hyperlink ref="G109" r:id="rId99"/>
+    <hyperlink ref="G110" r:id="rId100"/>
+    <hyperlink ref="G111" r:id="rId101"/>
+    <hyperlink ref="G112" r:id="rId102"/>
+    <hyperlink ref="G113" r:id="rId103"/>
+    <hyperlink ref="G114" r:id="rId104"/>
+    <hyperlink ref="G115" r:id="rId105"/>
+    <hyperlink ref="G116" r:id="rId106"/>
+    <hyperlink ref="G94" r:id="rId107"/>
     <hyperlink ref="G95" r:id="rId108"/>
     <hyperlink ref="G96" r:id="rId109"/>
+    <hyperlink ref="G97" r:id="rId110"/>
+    <hyperlink ref="G98" r:id="rId111"/>
+    <hyperlink ref="G99" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId110"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId113"/>
 </worksheet>
 </file>
--- a/apartments.xlsx
+++ b/apartments.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MASTER\Desktop\Bot_Eysk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MASTER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,14 +15,14 @@
     <sheet name="Объявления" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$I$1:$I$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$I$1:$I$100</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="414">
   <si>
     <t>ID</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>Большая полноценная кухня, холодильник, варочная поверхность, СВЧ, сплит-система, цифровое ТВ, стиральная машина, душевая кабина, постельные принадлежности, полотенца, Wi-fi(бесплатно), гладильная+утюг, посуда, мангал, беседка.</t>
-  </si>
-  <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_75492</t>
   </si>
   <si>
     <t>+7 921 259-58-02</t>
@@ -101,9 +98,6 @@
     <t>Наталья</t>
   </si>
   <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_75453</t>
-  </si>
-  <si>
     <t>Сдаётся светлая, уютная двухкомнатная квартира, все удобства, район стадиона, рядом центр, парк, море, хорошая транспортная развязка.</t>
   </si>
   <si>
@@ -122,22 +116,10 @@
     <t>Татьяна</t>
   </si>
   <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_65213</t>
-  </si>
-  <si>
     <t>Сдается дом 🏡 под ключ со всеми удобствами рядом с набережной🌊 Каменка, до пляжа Меляки🏖 5 минут, рядом аквапарк</t>
   </si>
   <si>
     <t>Анна</t>
-  </si>
-  <si>
-    <t>3-комн</t>
-  </si>
-  <si>
-    <t>Новый современный ремонт. Кухня на террасе. Во дворе батут,качели, песочница, игрушки. Каменка, парк, центр пешая доступность 7-10 минут. Рядом магнит, пятерочка, КБ. Парковка перед домом.</t>
-  </si>
-  <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_75128</t>
   </si>
   <si>
     <t>гостевой дом</t>
@@ -849,9 +831,6 @@
     <t>На территории есть: детская площадка, бассейн с подогревом для детей, батут.</t>
   </si>
   <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_66509</t>
-  </si>
-  <si>
     <t>Софья</t>
   </si>
   <si>
@@ -905,9 +884,6 @@
   </si>
   <si>
     <t>дом под ключ, без хозяев и соседей на территории. 2 изолиров комнаты, 6 спальных мест(можно поставить доп.место), все удобства</t>
-  </si>
-  <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_64781</t>
   </si>
   <si>
     <t>Свободен дом на Каменке , вместимость 3-6 чел. Ул Краснодарская/Октябрьская , чистый зеленый двор, качеля, песочница, беседка, мангальная зона. Перед двором стоянка под видео наблюдением.
@@ -1003,26 +979,7 @@
 👧👦Для маленьких гостей детская площадка , батут и много игрушек</t>
   </si>
   <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_63065</t>
-  </si>
-  <si>
     <t>+7 938 421-41-48</t>
-  </si>
-  <si>
-    <t>☀️Современные, уютные, светлые номера -студии у самой набережной
-☀️На территории сдается всего 4 номера
-☀️в каждом номере есть все необходимое для комфортного проживания :
-☀️кухня(эл. чайник, СВЧ, индукционная плита , посуда, холодильник)
-☀️ТВ и Wi-Fi
-☀️сплит-система
-☀️санузел
-☀️фен
-☀️шкаф
-☀️прикроватный столик
-☀️постельное белье
-☀️предметы гигиены (таул. бумага, осв. воздуха, губка для посуды )
-☀️спальные места (двуспальная кровать, двухъярусная кровать )
-☀️новые качественные матрасы для хорошего сна</t>
   </si>
   <si>
     <t>https://vk.com/eysk_aparts?w=wall-109406141_62990</t>
@@ -1124,16 +1081,7 @@
     <t>В квартире имеется вся необходимая мебель. Все вещи и бытовая техника для комфортного проживания имеется: утюг, телевизор с интернетом, быстрый интернет Wi-Fi, сплит-система, необходимая посуда. На кухне стол, стулья, кухонная стенка, электрическая плита, холодильник, чайник, микроволновая печь. Санузел совмещенный. Горячая и холодная вода всегда имеется.</t>
   </si>
   <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_59572</t>
-  </si>
-  <si>
     <t>+7 988 489-38-08</t>
-  </si>
-  <si>
-    <t>✨Двухкомнатный дом, до 5 человек со своим двориком, и зоной отдыха.
-В доме: Двуспальная кровать, ТВ, тумба в одной комнате; 2 односпальные кровати, шкаф в другой комнате, сплит система, WI-FI.
-Кухня: посуда, свч печь, холодильник, мультиварка, стир. машинка автомат.
-С/у и душ.</t>
   </si>
   <si>
     <t>В номере двуспальная кровать, двухъярусная кровать, сплит система, ТВ, комод, с/у и душ. К номерам есть балкон, столики, кухня, холодильник, свч печь, стир. машинка автомат</t>
@@ -1184,9 +1132,6 @@
   <si>
     <t>Дом 5 комнат, 2кухни, 2 санузла, зона отдыха, мангал, интернет. Предоставляется посуда, белье, полотенца,утюг.
 Есть все комфортного отдыха от 4—9 человек одной семьи или компании без других отдыхающих</t>
-  </si>
-  <si>
-    <t>https://vk.com/eysk_aparts?w=wall-109406141_44482</t>
   </si>
   <si>
     <t>В номерах есть все необходимое для комфортного проживания: кухня, плитка, холодильник, посуда, телевизор, Wi-fi, кондиционер в каждой комнате, сан. узел, душ, стиральная машинка, постельное белье, полотенца.
@@ -1524,6 +1469,104 @@
 💥Батуты🤸‍♀;
 📍В номерах на втором этаже есть всё необходимое для комфортного отдыха: Кухня, холодильник, чайник, посуда.
 Двуспальная кровать и двуспальный диван, тв, кондиционер, с/у и душ. К каждому номеру на балконе стол и сушилка для белья.</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76482</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76461</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76454</t>
+  </si>
+  <si>
+    <t>жилье 45 кВ.м (3 комнаты), свой отдельный дворик от хозяев, других отдыхающих нет. Кухня на террасе, мангал, батут, качели, песочница, игрушки. Парковка перед домом. Рядом магнит, пятерочка, КБ. Набережная со всеми развлечениями, Каменка, парк Поддубного и центр 7-10 мин пешком.</t>
+  </si>
+  <si>
+    <t>Фамилия</t>
+  </si>
+  <si>
+    <t>Минько</t>
+  </si>
+  <si>
+    <t>Кравченко</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76424</t>
+  </si>
+  <si>
+    <t>Альева</t>
+  </si>
+  <si>
+    <t>☀️Предлагаю для комфортного отдыха дом без хозяев для 3-5 человек и комнаты для 2х-4х человек ,со всеми удобствами
+☀️Район Приморской набережной-2 минуты ходьбы 🚶‍♀️,пляж 🏖-5 минут ходьбы.
+☀️рядом магазины🛍,кафе🍹,столовая 🍲,центральный рынок
+☀️большой выбор развлечений -аквапарк,океанариум,дельфинарий,парк аттракционов ,игровые палатки ,сувенирные лавки
+☀️парковка под видеонаблюдением</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76412</t>
+  </si>
+  <si>
+    <t>Григорьева</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76404</t>
+  </si>
+  <si>
+    <t>Широкова-Шитова</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76373</t>
+  </si>
+  <si>
+    <t>+7 912 080-14-89</t>
+  </si>
+  <si>
+    <t>Евгений</t>
+  </si>
+  <si>
+    <t>Ериков</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76363</t>
+  </si>
+  <si>
+    <t>🏖 До Ейского лимана — 1 минута пешком (70 метров)!
+Первая береговая линия, мелкое и тёплое море — идеально для отдыха с детьми.
+🏡 О доме
+площадь 35 м²
+две отдельные комнаты
+оборудованная кухня
+кондиционер
+телевизор
+холодильник
+Wi-Fi
+микроволновка
+электрочайник
+фен
+гладильная доска и утюг
+во дворе: мангал, просторный ухоженный двор
+туалет и душ во дворе рядом с домом</t>
+  </si>
+  <si>
+    <t>+7 961 515-15-00</t>
+  </si>
+  <si>
+    <t>Королькова</t>
+  </si>
+  <si>
+    <t>✔️Для летнего отдыха предлагается трехкомнатный дом до 6 чел.
+Зеленый двор, мангал, детский каркасный бассейн. Рядом парк с бесплатной детской площадкой - 3 мин., столовая - 5 мин.центр города, рынок - 10 мин. пляж Каменка- 15 мин. пешком.</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76348</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76318</t>
+  </si>
+  <si>
+    <t>https://vk.com/eysk_aparts?w=wall-109406141_76324</t>
   </si>
 </sst>
 </file>
@@ -1934,7 +1977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1946,15 +1989,16 @@
     <col min="7" max="7" width="50.44140625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="20.33203125" style="13" customWidth="1"/>
-    <col min="10" max="10" width="62.44140625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="17.77734375" style="13" customWidth="1"/>
+    <col min="11" max="11" width="62.44140625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1977,19 +2021,22 @@
       <c r="I1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2">
         <v>1000</v>
@@ -2009,16 +2056,17 @@
       <c r="I2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J2" s="3"/>
+      <c r="K2" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>15</v>
@@ -2033,7 +2081,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -2041,19 +2089,20 @@
       <c r="I3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="12"/>
+      <c r="K3" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2">
         <v>550</v>
@@ -2065,56 +2114,40 @@
         <v>13</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2">
-        <v>550</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
@@ -2129,24 +2162,25 @@
         <v>13</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>24</v>
+        <v>411</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="J6" s="12"/>
+      <c r="K6" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
@@ -2161,24 +2195,25 @@
         <v>13</v>
       </c>
       <c r="G7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="12"/>
+      <c r="K7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>15</v>
@@ -2193,24 +2228,25 @@
         <v>13</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="J8" s="12"/>
+      <c r="K8" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>15</v>
@@ -2225,27 +2261,28 @@
         <v>13</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2">
         <v>550</v>
@@ -2257,27 +2294,30 @@
         <v>13</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>36</v>
+        <v>390</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2">
         <v>250</v>
@@ -2289,24 +2329,25 @@
         <v>13</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>15</v>
@@ -2321,24 +2362,25 @@
         <v>13</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>15</v>
@@ -2353,27 +2395,28 @@
         <v>13</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="K13" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2">
         <v>700</v>
@@ -2382,27 +2425,28 @@
         <v>4</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="J14" s="12"/>
+      <c r="K14" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>15</v>
@@ -2414,30 +2458,31 @@
         <v>8</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="12"/>
+      <c r="K15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I15" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2">
         <v>350</v>
@@ -2446,30 +2491,31 @@
         <v>4</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="J16" s="12"/>
+      <c r="K16" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D17" s="2">
         <v>200</v>
@@ -2481,27 +2527,28 @@
         <v>13</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="J17" s="12"/>
+      <c r="K17" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2">
         <v>100</v>
@@ -2513,27 +2560,28 @@
         <v>13</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="J18" s="12"/>
+      <c r="K18" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D19" s="2">
         <v>300</v>
@@ -2545,27 +2593,28 @@
         <v>13</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+      <c r="J19" s="12"/>
+      <c r="K19" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
         <v>4</v>
@@ -2574,27 +2623,28 @@
         <v>13</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="J20" s="12"/>
+      <c r="K20" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D21" s="2">
         <v>50</v>
@@ -2606,24 +2656,25 @@
         <v>13</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="J21" s="12"/>
+      <c r="K21" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>11</v>
@@ -2638,27 +2689,28 @@
         <v>13</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="J22" s="12"/>
+      <c r="K22" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D23" s="2">
         <v>500</v>
@@ -2670,24 +2722,25 @@
         <v>13</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="J23" s="12"/>
+      <c r="K23" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>15</v>
@@ -2702,24 +2755,25 @@
         <v>13</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+      <c r="J24" s="12"/>
+      <c r="K24" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>15</v>
@@ -2734,27 +2788,28 @@
         <v>13</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="J25" s="12"/>
+      <c r="K25" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D26" s="2">
         <v>70</v>
@@ -2766,24 +2821,25 @@
         <v>13</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="J26" s="12"/>
+      <c r="K26" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>15</v>
@@ -2798,24 +2854,25 @@
         <v>13</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J27" s="12"/>
+      <c r="K27" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>15</v>
@@ -2830,27 +2887,28 @@
         <v>13</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="J28" s="12"/>
+      <c r="K28" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D29" s="2">
         <v>150</v>
@@ -2859,27 +2917,28 @@
         <v>4</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="J29" s="12"/>
+      <c r="K29" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>11</v>
@@ -2891,27 +2950,28 @@
         <v>4</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G30" s="9" t="s">
-        <v>109</v>
-      </c>
       <c r="H30" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="J30" s="12"/>
+      <c r="K30" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>31</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>15</v>
@@ -2923,27 +2983,28 @@
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="J31" s="12"/>
+      <c r="K31" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>15</v>
@@ -2958,27 +3019,28 @@
         <v>13</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="J32" s="12"/>
+      <c r="K32" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>33</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D33" s="2">
         <v>400</v>
@@ -2987,27 +3049,28 @@
         <v>4</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="J33" s="12"/>
+      <c r="K33" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>15</v>
@@ -3019,30 +3082,31 @@
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="J34" s="12"/>
+      <c r="K34" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I34" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D35" s="2">
         <v>1000</v>
@@ -3054,27 +3118,28 @@
         <v>13</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="J35" s="12"/>
+      <c r="K35" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>36</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D36" s="2">
         <v>400</v>
@@ -3083,27 +3148,28 @@
         <v>4</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+      <c r="J36" s="12"/>
+      <c r="K36" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>11</v>
@@ -3115,27 +3181,28 @@
         <v>4</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="J37" s="12"/>
+      <c r="K37" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>38</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>15</v>
@@ -3150,24 +3217,25 @@
         <v>13</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="J38" s="12"/>
+      <c r="K38" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>15</v>
@@ -3179,30 +3247,31 @@
         <v>6</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="J39" s="12"/>
+      <c r="K39" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>40</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D40" s="2">
         <v>300</v>
@@ -3214,24 +3283,25 @@
         <v>13</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="J40" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="J40" s="12"/>
+      <c r="K40" s="10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>8</v>
@@ -3246,24 +3316,25 @@
         <v>13</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+      <c r="J41" s="12"/>
+      <c r="K41" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>15</v>
@@ -3278,24 +3349,25 @@
         <v>13</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+      <c r="J42" s="12"/>
+      <c r="K42" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>8</v>
@@ -3310,27 +3382,28 @@
         <v>13</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+      <c r="J43" s="12"/>
+      <c r="K43" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>44</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D44" s="2">
         <v>800</v>
@@ -3342,24 +3415,25 @@
         <v>13</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="J44" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="J44" s="12"/>
+      <c r="K44" s="10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>45</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>15</v>
@@ -3374,24 +3448,25 @@
         <v>13</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="J45" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="J45" s="12"/>
+      <c r="K45" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>46</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>15</v>
@@ -3406,24 +3481,25 @@
         <v>13</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J46" s="10" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="J46" s="12"/>
+      <c r="K46" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>47</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>15</v>
@@ -3438,24 +3514,27 @@
         <v>13</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>48</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>8</v>
@@ -3470,24 +3549,25 @@
         <v>13</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="J48" s="12"/>
+      <c r="K48" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>49</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>15</v>
@@ -3502,24 +3582,25 @@
         <v>13</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="J49" s="12"/>
+      <c r="K49" s="10" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>50</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>15</v>
@@ -3531,27 +3612,28 @@
         <v>9</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+      <c r="J50" s="12"/>
+      <c r="K50" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>15</v>
@@ -3566,24 +3648,25 @@
         <v>13</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J51" s="10" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="J51" s="12"/>
+      <c r="K51" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>52</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>11</v>
@@ -3598,27 +3681,28 @@
         <v>13</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="J52" s="12"/>
+      <c r="K52" s="7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>53</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D53">
         <v>300</v>
@@ -3630,27 +3714,28 @@
         <v>13</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="J53" s="12"/>
+      <c r="K53" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>54</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D54" s="2">
         <v>750</v>
@@ -3662,27 +3747,28 @@
         <v>13</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+      <c r="J54" s="12"/>
+      <c r="K54" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>55</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D55">
         <v>70</v>
@@ -3694,27 +3780,28 @@
         <v>13</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="J55" s="10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="J55" s="12"/>
+      <c r="K55" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>56</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D56" s="2">
         <v>800</v>
@@ -3726,27 +3813,28 @@
         <v>13</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+      <c r="J56" s="12"/>
+      <c r="K56" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>58</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D57" s="2">
         <v>350</v>
@@ -3758,24 +3846,25 @@
         <v>13</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+      <c r="J57" s="12"/>
+      <c r="K57" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>59</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>15</v>
@@ -3790,27 +3879,28 @@
         <v>13</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="J58" s="12"/>
+      <c r="K58" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>60</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D59" s="2">
         <v>350</v>
@@ -3822,27 +3912,28 @@
         <v>13</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+      <c r="J59" s="12"/>
+      <c r="K59" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>61</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D60">
         <v>100</v>
@@ -3854,27 +3945,28 @@
         <v>13</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="J60" s="10" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="J60" s="12"/>
+      <c r="K60" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>62</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D61">
         <v>1000</v>
@@ -3886,24 +3978,25 @@
         <v>13</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+      <c r="J61" s="12"/>
+      <c r="K61" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>63</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>8</v>
@@ -3918,24 +4011,25 @@
         <v>13</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+      <c r="J62" s="12"/>
+      <c r="K62" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>64</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>15</v>
@@ -3950,27 +4044,28 @@
         <v>13</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J63" s="12"/>
+      <c r="K63" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>65</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D64">
         <v>1000</v>
@@ -3982,27 +4077,28 @@
         <v>13</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="J64" s="12"/>
+      <c r="K64" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>66</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D65">
         <v>500</v>
@@ -4014,27 +4110,28 @@
         <v>13</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>231</v>
+        <v>388</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+      <c r="J65" s="12"/>
+      <c r="K65" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>67</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D66">
         <v>20</v>
@@ -4046,24 +4143,25 @@
         <v>13</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J66" s="12"/>
+      <c r="K66" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>68</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>11</v>
@@ -4078,27 +4176,28 @@
         <v>13</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J67" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J67" s="12"/>
+      <c r="K67" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>69</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D68">
         <v>800</v>
@@ -4110,24 +4209,25 @@
         <v>13</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="J68" s="10" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+      <c r="J68" s="12"/>
+      <c r="K68" s="10" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>70</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>15</v>
@@ -4142,24 +4242,25 @@
         <v>13</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J69" s="7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="J69" s="12"/>
+      <c r="K69" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>71</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>15</v>
@@ -4174,24 +4275,27 @@
         <v>13</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>250</v>
+        <v>398</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J70" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="J70" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="K70" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>72</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>15</v>
@@ -4206,27 +4310,28 @@
         <v>13</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J71" s="10" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="J71" s="12"/>
+      <c r="K71" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>73</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D72">
         <v>400</v>
@@ -4238,24 +4343,25 @@
         <v>13</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="J72" s="10" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+      <c r="J72" s="12"/>
+      <c r="K72" s="10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>74</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>15</v>
@@ -4270,24 +4376,25 @@
         <v>13</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J73" s="10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="J73" s="12"/>
+      <c r="K73" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>75</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>11</v>
@@ -4299,30 +4406,31 @@
         <v>4</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+      <c r="J74" s="12"/>
+      <c r="K74" s="10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>76</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D75">
         <v>20</v>
@@ -4334,27 +4442,28 @@
         <v>13</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="I75" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J75" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J75" s="12"/>
+      <c r="K75" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>77</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D76">
         <v>200</v>
@@ -4366,27 +4475,28 @@
         <v>13</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I76" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="J76" s="12"/>
+      <c r="K76" s="10" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>78</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D77">
         <v>150</v>
@@ -4398,24 +4508,27 @@
         <v>13</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>270</v>
+        <v>395</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="I77" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J77" s="10" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J77" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="K77" s="10" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>79</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>15</v>
@@ -4430,24 +4543,25 @@
         <v>13</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="J78" s="10" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+      <c r="J78" s="12"/>
+      <c r="K78" s="10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>80</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>15</v>
@@ -4462,21 +4576,21 @@
         <v>13</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="J79" s="10" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+      <c r="K79" s="10" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>81</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>11</v>
@@ -4488,30 +4602,31 @@
         <v>4</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="I80" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="J80" s="10" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="J80" s="12"/>
+      <c r="K80" s="10" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>82</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D81">
         <v>500</v>
@@ -4523,27 +4638,28 @@
         <v>13</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I81" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="J81" s="10" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="J81" s="12"/>
+      <c r="K81" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>83</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D82">
         <v>400</v>
@@ -4552,30 +4668,31 @@
         <v>6</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J82" s="7" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="J82" s="12"/>
+      <c r="K82" s="7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>84</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D83">
         <v>750</v>
@@ -4584,30 +4701,31 @@
         <v>4</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J83" s="10" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="J83" s="12"/>
+      <c r="K83" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>85</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D84">
         <v>50</v>
@@ -4619,24 +4737,25 @@
         <v>13</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="J84" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+      <c r="J84" s="12"/>
+      <c r="K84" s="7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>86</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>11</v>
@@ -4648,126 +4767,130 @@
         <v>13</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J85" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+      <c r="J85" s="12"/>
+      <c r="K85" s="7" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D86">
         <v>300</v>
       </c>
       <c r="E86">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>301</v>
+        <v>389</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="I86" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J86" s="10" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J86" s="12"/>
+      <c r="K86" s="7" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D87">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+      <c r="J87" s="12"/>
+      <c r="K87" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D88">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="E88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="J88" s="7" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="J88" s="12"/>
+      <c r="K88" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D89">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="E89">
         <v>6</v>
@@ -4776,318 +4899,328 @@
         <v>13</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I89" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="J89" s="12"/>
+      <c r="K89" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>93</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D90">
+        <v>300</v>
+      </c>
+      <c r="E90">
+        <v>4</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I90" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J90" s="12"/>
+      <c r="K90" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>94</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91">
+        <v>500</v>
+      </c>
+      <c r="E91">
+        <v>9</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I91" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="J91" s="12"/>
+      <c r="K91" s="10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>95</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D92">
+        <v>50</v>
+      </c>
+      <c r="E92">
+        <v>4</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I92" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J92" s="12"/>
+      <c r="K92" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I89" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J89" s="10" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
-        <v>92</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C90" s="2" t="s">
+    </row>
+    <row r="93" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>96</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D93">
+        <v>500</v>
+      </c>
+      <c r="E93">
+        <v>5</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I93" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="J93" s="12"/>
+      <c r="K93" s="10" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>97</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D90">
-        <v>50</v>
-      </c>
-      <c r="E90">
-        <v>6</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="I90" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="J90" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
-        <v>93</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D91">
-        <v>300</v>
-      </c>
-      <c r="E91">
-        <v>4</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="I91" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="J91" s="7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <v>94</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D92">
-        <v>500</v>
-      </c>
-      <c r="E92">
-        <v>9</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="J92" s="10" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
-        <v>95</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D93">
-        <v>50</v>
-      </c>
-      <c r="E93">
-        <v>4</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="I93" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J93" s="10" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
-        <v>96</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D94">
         <v>500</v>
       </c>
       <c r="E94">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="J94" s="10" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+      <c r="J94" s="12"/>
+      <c r="K94" s="10" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D95">
         <v>500</v>
       </c>
       <c r="E95">
+        <v>4</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I95" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="J95" s="12"/>
+      <c r="K95" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>99</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D96">
+        <v>350</v>
+      </c>
+      <c r="E96">
         <v>7</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="9" t="s">
+      <c r="F96" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="I96" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="J96" s="12"/>
+      <c r="K96" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>100</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97">
+        <v>400</v>
+      </c>
+      <c r="E97">
+        <v>10</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I97" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="H95" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I95" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="J95" s="10" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="2">
-        <v>98</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D96">
-        <v>500</v>
-      </c>
-      <c r="E96">
-        <v>4</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96" s="9" t="s">
+      <c r="J97" s="12"/>
+      <c r="K97" s="10" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>101</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D98">
+        <v>800</v>
+      </c>
+      <c r="E98">
+        <v>5</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I98" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="J98" s="12"/>
+      <c r="K98" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="I96" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="J96" s="10" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="2">
-        <v>99</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D97">
-        <v>350</v>
-      </c>
-      <c r="E97">
-        <v>7</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="I97" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="J97" s="10" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
-        <v>100</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C98" s="2" t="s">
+    </row>
+    <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>102</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D98">
-        <v>400</v>
-      </c>
-      <c r="E98">
-        <v>10</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="I98" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="J98" s="10" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
-        <v>101</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="D99">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="E99">
         <v>5</v>
@@ -5096,29 +5229,57 @@
         <v>13</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="I99" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="J99" s="10" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="12"/>
-      <c r="J100" s="10"/>
-    </row>
-    <row r="101" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>404</v>
+      </c>
+      <c r="J99" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="K99" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>103</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100">
+        <v>900</v>
+      </c>
+      <c r="E100">
+        <v>6</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="I100" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="K100" s="10" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -5126,17 +5287,18 @@
       <c r="G101" s="9"/>
       <c r="H101" s="3"/>
       <c r="I101" s="12"/>
-      <c r="J101" s="10"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J101" s="12"/>
+      <c r="K101" s="10"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H102" s="3"/>
     </row>
-    <row r="103" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>15</v>
@@ -5148,30 +5310,30 @@
         <v>6</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="J103" s="10" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+      <c r="K103" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D104">
         <v>900</v>
@@ -5180,30 +5342,30 @@
         <v>3</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="J104" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+      <c r="K104" s="7" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D105">
         <v>900</v>
@@ -5215,24 +5377,24 @@
         <v>13</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J105" s="10" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="K105" s="10" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>15</v>
@@ -5247,27 +5409,27 @@
         <v>13</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="J106" s="7" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="K106" s="7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D107">
         <v>350</v>
@@ -5279,24 +5441,24 @@
         <v>13</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="J107" s="10" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="K107" s="10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>15</v>
@@ -5311,27 +5473,27 @@
         <v>13</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="I108" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="J108" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+      <c r="K108" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D109">
         <v>1200</v>
@@ -5343,27 +5505,27 @@
         <v>13</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="J109" s="10" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+      <c r="K109" s="10" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D110">
         <v>950</v>
@@ -5375,24 +5537,24 @@
         <v>13</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="I110" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J110" s="7" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="K110" s="7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>15</v>
@@ -5407,24 +5569,24 @@
         <v>13</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J111" s="10" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="K111" s="10" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>15</v>
@@ -5439,27 +5601,27 @@
         <v>13</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J112" s="10" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="K112" s="10" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D113">
         <v>450</v>
@@ -5468,27 +5630,27 @@
         <v>5</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="J113" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>15</v>
@@ -5500,27 +5662,27 @@
         <v>6</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J114" s="7" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="K114" s="7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>15</v>
@@ -5532,27 +5694,27 @@
         <v>6</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="J115" s="7" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>15</v>
@@ -5567,133 +5729,133 @@
         <v>13</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="J116" s="10" t="s">
-        <v>369</v>
+        <v>138</v>
+      </c>
+      <c r="K116" s="10" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="I1:I99"/>
+  <autoFilter ref="I1:I100"/>
   <hyperlinks>
     <hyperlink ref="G16" r:id="rId1"/>
     <hyperlink ref="G17" r:id="rId2"/>
     <hyperlink ref="G2" r:id="rId3"/>
     <hyperlink ref="G3" r:id="rId4"/>
     <hyperlink ref="G4" r:id="rId5"/>
-    <hyperlink ref="G5" r:id="rId6"/>
-    <hyperlink ref="G6" r:id="rId7"/>
-    <hyperlink ref="G7" r:id="rId8"/>
-    <hyperlink ref="G8" r:id="rId9"/>
-    <hyperlink ref="G9" r:id="rId10"/>
-    <hyperlink ref="G10" r:id="rId11"/>
-    <hyperlink ref="G11" r:id="rId12"/>
-    <hyperlink ref="G12" r:id="rId13"/>
-    <hyperlink ref="G13" r:id="rId14"/>
-    <hyperlink ref="G14" r:id="rId15"/>
-    <hyperlink ref="G15" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G23" r:id="rId22"/>
-    <hyperlink ref="G24" r:id="rId23"/>
-    <hyperlink ref="G25" r:id="rId24"/>
-    <hyperlink ref="G26" r:id="rId25"/>
-    <hyperlink ref="G27" r:id="rId26"/>
-    <hyperlink ref="G28" r:id="rId27"/>
-    <hyperlink ref="G29" r:id="rId28"/>
-    <hyperlink ref="G30" r:id="rId29"/>
-    <hyperlink ref="G31" r:id="rId30"/>
-    <hyperlink ref="G32" r:id="rId31"/>
-    <hyperlink ref="G33" r:id="rId32"/>
-    <hyperlink ref="G34" r:id="rId33"/>
-    <hyperlink ref="G35" r:id="rId34"/>
-    <hyperlink ref="G36" r:id="rId35"/>
-    <hyperlink ref="G37" r:id="rId36"/>
-    <hyperlink ref="G38" r:id="rId37"/>
-    <hyperlink ref="G39" r:id="rId38"/>
-    <hyperlink ref="G40" r:id="rId39"/>
-    <hyperlink ref="G41" r:id="rId40"/>
-    <hyperlink ref="G42" r:id="rId41"/>
-    <hyperlink ref="G43" r:id="rId42"/>
-    <hyperlink ref="G44" r:id="rId43"/>
-    <hyperlink ref="G45" r:id="rId44"/>
-    <hyperlink ref="G46" r:id="rId45"/>
-    <hyperlink ref="G47" r:id="rId46"/>
-    <hyperlink ref="G48" r:id="rId47"/>
-    <hyperlink ref="G49" r:id="rId48"/>
-    <hyperlink ref="G50" r:id="rId49"/>
-    <hyperlink ref="G51" r:id="rId50"/>
-    <hyperlink ref="G52" r:id="rId51"/>
-    <hyperlink ref="G53" r:id="rId52"/>
-    <hyperlink ref="G54" r:id="rId53"/>
-    <hyperlink ref="G55" r:id="rId54"/>
-    <hyperlink ref="G56" r:id="rId55"/>
-    <hyperlink ref="G57" r:id="rId56"/>
-    <hyperlink ref="G58" r:id="rId57"/>
-    <hyperlink ref="G59" r:id="rId58"/>
-    <hyperlink ref="G60" r:id="rId59"/>
-    <hyperlink ref="G61" r:id="rId60"/>
-    <hyperlink ref="G62" r:id="rId61"/>
-    <hyperlink ref="G63" r:id="rId62"/>
-    <hyperlink ref="G64" r:id="rId63"/>
-    <hyperlink ref="G65" r:id="rId64"/>
-    <hyperlink ref="G66" r:id="rId65"/>
-    <hyperlink ref="G67" r:id="rId66"/>
-    <hyperlink ref="G68" r:id="rId67"/>
-    <hyperlink ref="G69" r:id="rId68"/>
-    <hyperlink ref="G70" r:id="rId69"/>
-    <hyperlink ref="G71" r:id="rId70"/>
-    <hyperlink ref="G72" r:id="rId71"/>
-    <hyperlink ref="G73" r:id="rId72"/>
-    <hyperlink ref="G74" r:id="rId73"/>
-    <hyperlink ref="G75" r:id="rId74"/>
-    <hyperlink ref="G76" r:id="rId75"/>
-    <hyperlink ref="G77" r:id="rId76"/>
-    <hyperlink ref="G78" r:id="rId77"/>
-    <hyperlink ref="G79" r:id="rId78"/>
-    <hyperlink ref="G80" r:id="rId79"/>
-    <hyperlink ref="G81" r:id="rId80"/>
-    <hyperlink ref="G82" r:id="rId81"/>
-    <hyperlink ref="G83" r:id="rId82"/>
-    <hyperlink ref="G84" r:id="rId83"/>
-    <hyperlink ref="G85" r:id="rId84"/>
-    <hyperlink ref="G86" r:id="rId85"/>
-    <hyperlink ref="G87" r:id="rId86"/>
-    <hyperlink ref="G88" r:id="rId87"/>
-    <hyperlink ref="G89" r:id="rId88"/>
-    <hyperlink ref="G90" r:id="rId89"/>
-    <hyperlink ref="G91" r:id="rId90"/>
-    <hyperlink ref="G92" r:id="rId91"/>
-    <hyperlink ref="G93" r:id="rId92"/>
-    <hyperlink ref="G103" r:id="rId93"/>
-    <hyperlink ref="G104" r:id="rId94"/>
-    <hyperlink ref="G105" r:id="rId95"/>
-    <hyperlink ref="G106" r:id="rId96"/>
-    <hyperlink ref="G107" r:id="rId97"/>
-    <hyperlink ref="G108" r:id="rId98"/>
-    <hyperlink ref="G109" r:id="rId99"/>
-    <hyperlink ref="G110" r:id="rId100"/>
-    <hyperlink ref="G111" r:id="rId101"/>
-    <hyperlink ref="G112" r:id="rId102"/>
-    <hyperlink ref="G113" r:id="rId103"/>
-    <hyperlink ref="G114" r:id="rId104"/>
-    <hyperlink ref="G115" r:id="rId105"/>
-    <hyperlink ref="G116" r:id="rId106"/>
-    <hyperlink ref="G94" r:id="rId107"/>
-    <hyperlink ref="G95" r:id="rId108"/>
-    <hyperlink ref="G96" r:id="rId109"/>
-    <hyperlink ref="G97" r:id="rId110"/>
-    <hyperlink ref="G98" r:id="rId111"/>
-    <hyperlink ref="G99" r:id="rId112"/>
+    <hyperlink ref="G6" r:id="rId6"/>
+    <hyperlink ref="G7" r:id="rId7"/>
+    <hyperlink ref="G8" r:id="rId8"/>
+    <hyperlink ref="G9" r:id="rId9"/>
+    <hyperlink ref="G10" r:id="rId10"/>
+    <hyperlink ref="G11" r:id="rId11"/>
+    <hyperlink ref="G12" r:id="rId12"/>
+    <hyperlink ref="G13" r:id="rId13"/>
+    <hyperlink ref="G14" r:id="rId14"/>
+    <hyperlink ref="G15" r:id="rId15"/>
+    <hyperlink ref="G18" r:id="rId16"/>
+    <hyperlink ref="G19" r:id="rId17"/>
+    <hyperlink ref="G20" r:id="rId18"/>
+    <hyperlink ref="G21" r:id="rId19"/>
+    <hyperlink ref="G22" r:id="rId20"/>
+    <hyperlink ref="G23" r:id="rId21"/>
+    <hyperlink ref="G24" r:id="rId22"/>
+    <hyperlink ref="G25" r:id="rId23"/>
+    <hyperlink ref="G26" r:id="rId24"/>
+    <hyperlink ref="G27" r:id="rId25"/>
+    <hyperlink ref="G28" r:id="rId26"/>
+    <hyperlink ref="G29" r:id="rId27"/>
+    <hyperlink ref="G30" r:id="rId28"/>
+    <hyperlink ref="G31" r:id="rId29"/>
+    <hyperlink ref="G32" r:id="rId30"/>
+    <hyperlink ref="G33" r:id="rId31"/>
+    <hyperlink ref="G34" r:id="rId32"/>
+    <hyperlink ref="G35" r:id="rId33"/>
+    <hyperlink ref="G36" r:id="rId34"/>
+    <hyperlink ref="G37" r:id="rId35"/>
+    <hyperlink ref="G38" r:id="rId36"/>
+    <hyperlink ref="G39" r:id="rId37"/>
+    <hyperlink ref="G40" r:id="rId38"/>
+    <hyperlink ref="G41" r:id="rId39"/>
+    <hyperlink ref="G42" r:id="rId40"/>
+    <hyperlink ref="G43" r:id="rId41"/>
+    <hyperlink ref="G44" r:id="rId42"/>
+    <hyperlink ref="G45" r:id="rId43"/>
+    <hyperlink ref="G46" r:id="rId44"/>
+    <hyperlink ref="G47" r:id="rId45"/>
+    <hyperlink ref="G48" r:id="rId46"/>
+    <hyperlink ref="G49" r:id="rId47"/>
+    <hyperlink ref="G50" r:id="rId48"/>
+    <hyperlink ref="G51" r:id="rId49"/>
+    <hyperlink ref="G52" r:id="rId50"/>
+    <hyperlink ref="G53" r:id="rId51"/>
+    <hyperlink ref="G54" r:id="rId52"/>
+    <hyperlink ref="G55" r:id="rId53"/>
+    <hyperlink ref="G56" r:id="rId54"/>
+    <hyperlink ref="G57" r:id="rId55"/>
+    <hyperlink ref="G58" r:id="rId56"/>
+    <hyperlink ref="G59" r:id="rId57"/>
+    <hyperlink ref="G60" r:id="rId58"/>
+    <hyperlink ref="G61" r:id="rId59"/>
+    <hyperlink ref="G62" r:id="rId60"/>
+    <hyperlink ref="G63" r:id="rId61"/>
+    <hyperlink ref="G64" r:id="rId62"/>
+    <hyperlink ref="G65" r:id="rId63"/>
+    <hyperlink ref="G66" r:id="rId64"/>
+    <hyperlink ref="G67" r:id="rId65"/>
+    <hyperlink ref="G68" r:id="rId66"/>
+    <hyperlink ref="G69" r:id="rId67"/>
+    <hyperlink ref="G70" r:id="rId68"/>
+    <hyperlink ref="G71" r:id="rId69"/>
+    <hyperlink ref="G72" r:id="rId70"/>
+    <hyperlink ref="G73" r:id="rId71"/>
+    <hyperlink ref="G74" r:id="rId72"/>
+    <hyperlink ref="G75" r:id="rId73"/>
+    <hyperlink ref="G76" r:id="rId74"/>
+    <hyperlink ref="G77" r:id="rId75"/>
+    <hyperlink ref="G78" r:id="rId76"/>
+    <hyperlink ref="G79" r:id="rId77"/>
+    <hyperlink ref="G80" r:id="rId78"/>
+    <hyperlink ref="G81" r:id="rId79"/>
+    <hyperlink ref="G82" r:id="rId80"/>
+    <hyperlink ref="G83" r:id="rId81"/>
+    <hyperlink ref="G84" r:id="rId82"/>
+    <hyperlink ref="G85" r:id="rId83"/>
+    <hyperlink ref="G86" r:id="rId84"/>
+    <hyperlink ref="G87" r:id="rId85"/>
+    <hyperlink ref="G88" r:id="rId86"/>
+    <hyperlink ref="G89" r:id="rId87"/>
+    <hyperlink ref="G90" r:id="rId88"/>
+    <hyperlink ref="G91" r:id="rId89"/>
+    <hyperlink ref="G92" r:id="rId90"/>
+    <hyperlink ref="G103" r:id="rId91"/>
+    <hyperlink ref="G104" r:id="rId92"/>
+    <hyperlink ref="G105" r:id="rId93"/>
+    <hyperlink ref="G106" r:id="rId94"/>
+    <hyperlink ref="G107" r:id="rId95"/>
+    <hyperlink ref="G108" r:id="rId96"/>
+    <hyperlink ref="G109" r:id="rId97"/>
+    <hyperlink ref="G110" r:id="rId98"/>
+    <hyperlink ref="G111" r:id="rId99"/>
+    <hyperlink ref="G112" r:id="rId100"/>
+    <hyperlink ref="G113" r:id="rId101"/>
+    <hyperlink ref="G114" r:id="rId102"/>
+    <hyperlink ref="G115" r:id="rId103"/>
+    <hyperlink ref="G116" r:id="rId104"/>
+    <hyperlink ref="G93" r:id="rId105"/>
+    <hyperlink ref="G94" r:id="rId106"/>
+    <hyperlink ref="G95" r:id="rId107"/>
+    <hyperlink ref="G96" r:id="rId108"/>
+    <hyperlink ref="G97" r:id="rId109"/>
+    <hyperlink ref="G98" r:id="rId110"/>
+    <hyperlink ref="G99" r:id="rId111"/>
+    <hyperlink ref="G100" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId113"/>
